--- a/reports/빅딜/history/2026-05-07/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-05-07/빅딜_training_mgf_report.xlsx
@@ -22,16 +22,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">밀크런!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">초코나라!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">털미녀!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">털미녀!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="658">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>251</t>
+    <t>250</t>
   </si>
   <si>
     <t>6위</t>
@@ -138,7 +138,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>354</t>
+    <t>355</t>
   </si>
   <si>
     <t>13위</t>
@@ -183,13 +183,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>352</t>
+    <t>353</t>
   </si>
   <si>
     <t>29위</t>
   </si>
   <si>
-    <t>466조 182억 7111만</t>
+    <t>466조 9065억 7092만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 3조 이상 일일기부 300+ 길컨 참여자</t>
@@ -207,7 +207,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>896</t>
+    <t>895</t>
   </si>
   <si>
     <t>8위</t>
@@ -231,16 +231,16 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>1855</t>
+    <t>1842</t>
   </si>
   <si>
     <t>100위</t>
   </si>
   <si>
-    <t>25명</t>
-  </si>
-  <si>
-    <t>30조 4755억 7052만</t>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>30조 8935억 1105만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요 길갑문의 : 정뽀</t>
@@ -951,7 +951,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 2505억 7149만</t>
+    <t>1조 2515억 213만</t>
   </si>
   <si>
     <t>울힝</t>
@@ -963,6 +963,12 @@
     <t>100조 3090억 1722만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>61조 9128억 5605만</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -972,12 +978,6 @@
     <t>60조 9099억 5542만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>48조 3007억 2445만</t>
-  </si>
-  <si>
     <t>큐샤프</t>
   </si>
   <si>
@@ -1089,6 +1089,24 @@
     <t>8조 353억 2065만</t>
   </si>
   <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>7조 9942억 9967만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>7조 7632억 9651만</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
@@ -1125,6 +1143,15 @@
     <t>5조 7027억 3580만</t>
   </si>
   <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>5조 3996억 7064만</t>
+  </si>
+  <si>
     <t>민들레꽃</t>
   </si>
   <si>
@@ -1161,6 +1188,24 @@
     <t>3조 4127억 6119만</t>
   </si>
   <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>3조 3267억 9445만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 8773억 332만</t>
+  </si>
+  <si>
     <t>제스프리</t>
   </si>
   <si>
@@ -1506,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>13조 5792억 6362만</t>
+    <t>14조 806억 5546만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1542,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=Scope</t>
   </si>
   <si>
-    <t>5조 371억 5749만</t>
+    <t>5조 778억 5430만</t>
   </si>
   <si>
     <t>하콩치</t>
@@ -1809,15 +1854,6 @@
     <t>1조 4367억 7349만</t>
   </si>
   <si>
-    <t>비숍마로밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%A7%88%EB%A1%9C%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>1조 3524억 1430만</t>
-  </si>
-  <si>
     <t>존못에겐남짱</t>
   </si>
   <si>
@@ -1905,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>2조 9376억 8402만</t>
+    <t>2조 9491억 9309만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1965,10 +2001,10 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>8453만</t>
+    <t>68</t>
+  </si>
+  <si>
+    <t>1억 1160만</t>
   </si>
 </sst>
 </file>
@@ -4778,7 +4814,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4862,25 +4898,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -4894,22 +4930,22 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>313</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>314</v>
@@ -5322,10 +5358,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>354</v>
@@ -5354,7 +5390,7 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>186</v>
@@ -5389,7 +5425,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>360</v>
@@ -5418,10 +5454,10 @@
         <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>363</v>
@@ -5450,10 +5486,10 @@
         <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>366</v>
@@ -5482,10 +5518,10 @@
         <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>369</v>
@@ -5517,7 +5553,7 @@
         <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>372</v>
@@ -5546,7 +5582,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>326</v>
+        <v>156</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>117</v>
@@ -5578,10 +5614,10 @@
         <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>378</v>
@@ -5610,10 +5646,10 @@
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>381</v>
@@ -5622,8 +5658,168 @@
         <v>23</v>
       </c>
     </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5650,6 +5846,11 @@
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5716,7 +5917,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>142</v>
@@ -5728,7 +5929,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -5742,13 +5943,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -5760,7 +5961,7 @@
         <v>122</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -5774,13 +5975,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -5792,7 +5993,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -5806,13 +6007,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -5824,7 +6025,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -5838,13 +6039,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -5856,7 +6057,7 @@
         <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -5870,13 +6071,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -5888,7 +6089,7 @@
         <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -5902,13 +6103,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -5920,7 +6121,7 @@
         <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -5934,13 +6135,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -5952,7 +6153,7 @@
         <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -5966,13 +6167,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -5984,7 +6185,7 @@
         <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -5998,13 +6199,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
@@ -6016,7 +6217,7 @@
         <v>117</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -6030,13 +6231,13 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -6048,7 +6249,7 @@
         <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -6062,13 +6263,13 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -6080,7 +6281,7 @@
         <v>122</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -6094,13 +6295,13 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -6112,7 +6313,7 @@
         <v>122</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -6126,13 +6327,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
@@ -6144,7 +6345,7 @@
         <v>117</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -6158,13 +6359,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -6176,7 +6377,7 @@
         <v>117</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -6190,13 +6391,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -6208,7 +6409,7 @@
         <v>117</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -6222,13 +6423,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
@@ -6240,7 +6441,7 @@
         <v>117</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -6254,13 +6455,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
@@ -6272,7 +6473,7 @@
         <v>122</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -6286,13 +6487,13 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
@@ -6304,7 +6505,7 @@
         <v>122</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
@@ -6318,13 +6519,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
@@ -6336,7 +6537,7 @@
         <v>117</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -6350,13 +6551,13 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
@@ -6368,7 +6569,7 @@
         <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
@@ -6382,13 +6583,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
@@ -6400,7 +6601,7 @@
         <v>122</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
@@ -6414,13 +6615,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -6432,7 +6633,7 @@
         <v>122</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
@@ -6446,13 +6647,13 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -6464,7 +6665,7 @@
         <v>122</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
@@ -6478,13 +6679,13 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
@@ -6496,7 +6697,7 @@
         <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>23</v>
@@ -6510,13 +6711,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
@@ -6528,7 +6729,7 @@
         <v>117</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>23</v>
@@ -6542,13 +6743,13 @@
         <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -6560,7 +6761,7 @@
         <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>23</v>
@@ -6574,13 +6775,13 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
@@ -6592,7 +6793,7 @@
         <v>186</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>23</v>
@@ -6606,13 +6807,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
@@ -6624,7 +6825,7 @@
         <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>23</v>
@@ -6638,13 +6839,13 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>83</v>
@@ -6653,10 +6854,10 @@
         <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>23</v>
@@ -6755,13 +6956,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>83</v>
@@ -6773,7 +6974,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -6787,13 +6988,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -6805,7 +7006,7 @@
         <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -6819,13 +7020,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -6837,7 +7038,7 @@
         <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -6851,13 +7052,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -6869,7 +7070,7 @@
         <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -6889,7 +7090,7 @@
         <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>142</v>
@@ -6901,7 +7102,7 @@
         <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -6915,13 +7116,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -6933,7 +7134,7 @@
         <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -6947,13 +7148,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -6965,7 +7166,7 @@
         <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -6979,13 +7180,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -6997,7 +7198,7 @@
         <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -7011,13 +7212,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -7029,7 +7230,7 @@
         <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -7043,13 +7244,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
@@ -7061,7 +7262,7 @@
         <v>122</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -7075,13 +7276,13 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -7090,10 +7291,10 @@
         <v>116</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -7107,13 +7308,13 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -7125,7 +7326,7 @@
         <v>117</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -7139,13 +7340,13 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -7157,7 +7358,7 @@
         <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -7171,13 +7372,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
@@ -7189,7 +7390,7 @@
         <v>186</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -7203,13 +7404,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -7221,7 +7422,7 @@
         <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -7235,13 +7436,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -7253,7 +7454,7 @@
         <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -7267,13 +7468,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
@@ -7285,7 +7486,7 @@
         <v>203</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -7318,7 +7519,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7377,19 +7578,19 @@
         <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>142</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -7403,25 +7604,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -7435,13 +7636,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -7453,7 +7654,7 @@
         <v>186</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -7467,13 +7668,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -7485,7 +7686,7 @@
         <v>186</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -7499,13 +7700,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -7517,7 +7718,7 @@
         <v>186</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -7531,13 +7732,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -7549,7 +7750,7 @@
         <v>186</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -7563,13 +7764,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -7581,7 +7782,7 @@
         <v>186</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -7595,13 +7796,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -7613,7 +7814,7 @@
         <v>186</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -7627,13 +7828,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
@@ -7645,7 +7846,7 @@
         <v>186</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -7659,13 +7860,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
@@ -7677,7 +7878,7 @@
         <v>186</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -7691,13 +7892,13 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -7709,7 +7910,7 @@
         <v>186</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -7723,13 +7924,13 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>83</v>
@@ -7741,7 +7942,7 @@
         <v>186</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -7755,13 +7956,13 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -7773,7 +7974,7 @@
         <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -7787,13 +7988,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>83</v>
@@ -7805,7 +8006,7 @@
         <v>216</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -7819,13 +8020,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>83</v>
@@ -7837,7 +8038,7 @@
         <v>216</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -7851,13 +8052,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -7869,7 +8070,7 @@
         <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -7883,13 +8084,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>83</v>
@@ -7901,7 +8102,7 @@
         <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -7915,13 +8116,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>83</v>
@@ -7933,7 +8134,7 @@
         <v>203</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -7947,13 +8148,13 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>83</v>
@@ -7965,7 +8166,7 @@
         <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
@@ -7979,13 +8180,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>83</v>
@@ -7997,7 +8198,7 @@
         <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -8011,13 +8212,13 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
@@ -8029,7 +8230,7 @@
         <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
@@ -8043,13 +8244,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>83</v>
@@ -8058,10 +8259,10 @@
         <v>116</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
@@ -8075,13 +8276,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -8093,7 +8294,7 @@
         <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
@@ -8107,13 +8308,13 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -8125,7 +8326,7 @@
         <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
@@ -8139,25 +8340,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>90</v>
+        <v>538</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>612</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>23</v>
@@ -8171,25 +8372,25 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>600</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>23</v>
@@ -8203,25 +8404,25 @@
         <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>203</v>
+        <v>612</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>23</v>
@@ -8235,25 +8436,25 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>23</v>
@@ -8267,13 +8468,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
@@ -8282,49 +8483,17 @@
         <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8355,7 +8524,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8422,7 +8590,7 @@
         <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>142</v>
@@ -8434,7 +8602,7 @@
         <v>122</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -8448,25 +8616,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -8480,13 +8648,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -8498,7 +8666,7 @@
         <v>186</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -8512,13 +8680,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -8530,7 +8698,7 @@
         <v>186</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -8544,13 +8712,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
@@ -8562,7 +8730,7 @@
         <v>186</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -8576,13 +8744,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -8594,7 +8762,7 @@
         <v>203</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -8608,13 +8776,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>83</v>
@@ -8626,7 +8794,7 @@
         <v>216</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -8640,13 +8808,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>83</v>
@@ -8655,10 +8823,10 @@
         <v>143</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -8672,25 +8840,25 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -8704,25 +8872,25 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
